--- a/data/suspension/Comparison Example/Phone B gyroscope shifted.xlsx
+++ b/data/suspension/Comparison Example/Phone B gyroscope shifted.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Raw Data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata Device" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metadata Time" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45658,7 +45659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45720,12 +45721,106 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>clock_error_s</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Values are copied unchanged; only the time column was moved and trimmed. Adding 2.4 s to this file's time column restores the original timing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>clock_note</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>The recorded start timestamp is -0.9 s away from the real start, imitating a phone clock that is not synchronised.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>experiment time</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>system time</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>system time text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1784628992.908968</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-07-21 12:16:32.908 UTC+02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PAUSE</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>26.54823529175483</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1784629019.457203</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-07-21 12:16:59.457 UTC+02:00</t>
         </is>
       </c>
     </row>
